--- a/clients/encore/testcases/discount-matrix/discount-matrix-company-matrix.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-company-matrix.xlsx
@@ -761,7 +761,7 @@
     <t>Last Updated: 2026-08-21</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>
